--- a/artfynd/A 36810-2025 artfynd.xlsx
+++ b/artfynd/A 36810-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,54 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>16579341</v>
+        <v>498635</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91394</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>2051</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Kytöv. &amp; M.Toivonen</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skjutbanebergsheden, Ång</t>
+          <t>Skjutbaneberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>727783.6548983046</v>
+        <v>727814</v>
       </c>
       <c r="R2" t="n">
-        <v>7073685.494054832</v>
+        <v>7073756</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +749,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2014-08-06</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-09-04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2014-08-06</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-09-04</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Mestadels mossig, men bitvis mycket fin lavtallhed, olikåldrig med många gamla träd, delar av området nyligen gallrat, med riset liggande kvar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,71 +770,61 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>sandtallskog</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Jonas F Grahn</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Irene Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>16579343</v>
+        <v>1841089</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90691</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6276</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skjutbanebergsheden, Ång</t>
+          <t>Skjutbaneberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>727723.5954369125</v>
+        <v>727814</v>
       </c>
       <c r="R3" t="n">
-        <v>7073690.932219391</v>
+        <v>7073756</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,22 +851,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2014-08-06</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-09-04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2014-08-06</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-09-04</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Mestadels mossig, men bitvis mycket fin lavtallhed, olikåldrig med många gamla träd, delar av området nyligen gallrat, med riset liggande kvar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,76 +872,61 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>sandtallskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Jonas F Grahn</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Andreas Garpebring</t>
+          <t>Irene Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>16579342</v>
+        <v>16579341</v>
       </c>
       <c r="B4" t="n">
-        <v>4717</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102306</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skjutbanebergsheden, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>727720.5807561408</v>
+        <v>727784</v>
       </c>
       <c r="R4" t="n">
-        <v>7073701.831149709</v>
+        <v>7073685</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,21 +956,11 @@
           <t>2014-08-06</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2014-08-06</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1014,11 +973,6 @@
       <c r="AI4" t="inlineStr">
         <is>
           <t>sandtallskog</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>gran</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1033,6 +987,220 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>16579343</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Skjutbanebergsheden, Ång</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>727724</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7073691</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2014-08-06</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2014-08-06</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>sandtallskog</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>16579342</v>
+      </c>
+      <c r="B6" t="n">
+        <v>4781</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Skjutbanebergsheden, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>727721</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7073702</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2014-08-06</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2014-08-06</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>sandtallskog</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Andreas Garpebring</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 36810-2025 artfynd.xlsx
+++ b/artfynd/A 36810-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/498635</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,6 +895,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1841089</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16579341</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1089,6 +1109,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16579343</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1201,8 +1226,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16579342</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>